--- a/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
+++ b/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sreekanth/work/moj/ex-ui/ccd_def/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sreekanth/work/moj/ex-ui/rpx-xui-webapp/test_codecept/e2e/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D4D39C-E1D7-4344-94A4-08521F2DBC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDA13CF9-2A06-2946-9523-6111C0648949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurisdiction" sheetId="1" r:id="rId1"/>
@@ -9767,7 +9767,7 @@
         <v>27</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>197</v>

--- a/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
+++ b/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sreekanth/work/moj/ex-ui/rpx-xui-webapp/test_codecept/e2e/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDA13CF9-2A06-2946-9523-6111C0648949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA2230-70FB-0945-B9DC-5ABB01D06A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurisdiction" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="386">
   <si>
     <t>Jurisdiction</t>
   </si>
@@ -8544,7 +8544,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -9758,23 +9758,25 @@
         <v>384</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E28" s="72" t="s">
-        <v>382</v>
+        <v>198</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="F28" s="21">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I28" s="12"/>
+        <v>187</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>188</v>
+      </c>
       <c r="J28" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -9802,13 +9804,13 @@
         <v>198</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F29" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>187</v>
@@ -9820,18 +9822,18 @@
         <v>1</v>
       </c>
       <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
       <c r="N29" s="7"/>
       <c r="O29" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
-      <c r="U29" s="27"/>
+      <c r="U29" s="30"/>
     </row>
     <row r="30" spans="1:21" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
@@ -9845,10 +9847,10 @@
         <v>198</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F30" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>190</v>
@@ -9867,14 +9869,13 @@
       <c r="M30" s="12"/>
       <c r="N30" s="7"/>
       <c r="O30" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
-      <c r="U30" s="30"/>
     </row>
     <row r="31" spans="1:21" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
@@ -9888,10 +9889,10 @@
         <v>198</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F31" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>190</v>
@@ -9907,10 +9908,10 @@
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
+      <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -9930,10 +9931,10 @@
         <v>198</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F32" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>190</v>
@@ -9949,10 +9950,10 @@
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="12"/>
-      <c r="M32" s="7"/>
+      <c r="M32" s="12"/>
       <c r="N32" s="7"/>
       <c r="O32" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
@@ -9972,10 +9973,10 @@
         <v>198</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F33" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>190</v>
@@ -9994,7 +9995,7 @@
       <c r="M33" s="12"/>
       <c r="N33" s="7"/>
       <c r="O33" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
@@ -10014,29 +10015,29 @@
         <v>198</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F34" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>190</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J34" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
       <c r="N34" s="7"/>
       <c r="O34" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
@@ -10056,10 +10057,10 @@
         <v>198</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F35" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>190</v>
@@ -10078,7 +10079,7 @@
       <c r="M35" s="12"/>
       <c r="N35" s="7"/>
       <c r="O35" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
@@ -10098,10 +10099,10 @@
         <v>198</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F36" s="21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>190</v>
@@ -10120,7 +10121,7 @@
       <c r="M36" s="12"/>
       <c r="N36" s="7"/>
       <c r="O36" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
@@ -10140,10 +10141,10 @@
         <v>198</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F37" s="21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>190</v>
@@ -10162,7 +10163,7 @@
       <c r="M37" s="12"/>
       <c r="N37" s="7"/>
       <c r="O37" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
@@ -10182,10 +10183,10 @@
         <v>198</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F38" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>190</v>
@@ -10224,29 +10225,29 @@
         <v>198</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F39" s="21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>190</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J39" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
       <c r="N39" s="7"/>
       <c r="O39" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
@@ -10266,13 +10267,13 @@
         <v>198</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F40" s="21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>195</v>
@@ -10284,11 +10285,11 @@
         <v>3</v>
       </c>
       <c r="K40" s="7"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
@@ -10308,10 +10309,10 @@
         <v>198</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F41" s="21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>186</v>
@@ -10330,7 +10331,7 @@
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
@@ -10350,10 +10351,10 @@
         <v>198</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F42" s="21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>186</v>
@@ -10372,7 +10373,7 @@
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
@@ -10392,10 +10393,10 @@
         <v>198</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F43" s="21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>186</v>
@@ -10414,7 +10415,7 @@
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
@@ -10434,10 +10435,10 @@
         <v>198</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F44" s="21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>186</v>
@@ -10456,7 +10457,7 @@
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
       <c r="O44" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
@@ -10476,22 +10477,20 @@
         <v>198</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F45" s="21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>186</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>196</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="I45" s="12"/>
       <c r="J45" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -10518,10 +10517,10 @@
         <v>198</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F46" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>186</v>
@@ -10538,7 +10537,7 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
@@ -10558,13 +10557,13 @@
         <v>198</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F47" s="21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>197</v>
@@ -10578,7 +10577,7 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
@@ -10597,14 +10596,14 @@
       <c r="D48" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>114</v>
+      <c r="E48" s="62" t="s">
+        <v>117</v>
       </c>
       <c r="F48" s="21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>197</v>
@@ -10618,7 +10617,7 @@
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P48" s="7"/>
       <c r="Q48" s="7"/>
@@ -10637,11 +10636,11 @@
       <c r="D49" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="E49" s="62" t="s">
-        <v>117</v>
+      <c r="E49" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="F49" s="21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>186</v>
@@ -10658,7 +10657,7 @@
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
       <c r="O49" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
@@ -10678,10 +10677,10 @@
         <v>198</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F50" s="21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>186</v>
@@ -10689,7 +10688,7 @@
       <c r="H50" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I50" s="12"/>
+      <c r="I50" s="7"/>
       <c r="J50" s="21">
         <v>4</v>
       </c>
@@ -10698,7 +10697,7 @@
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
       <c r="O50" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
@@ -10718,10 +10717,10 @@
         <v>198</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F51" s="21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>186</v>
@@ -10729,7 +10728,7 @@
       <c r="H51" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I51" s="7"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="21">
         <v>4</v>
       </c>
@@ -10738,7 +10737,7 @@
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
@@ -10754,22 +10753,24 @@
       <c r="C52" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>123</v>
+      <c r="D52" s="63" t="s">
+        <v>354</v>
+      </c>
+      <c r="E52" s="62" t="s">
+        <v>373</v>
       </c>
       <c r="F52" s="21">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H52" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H52" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="I52" s="12"/>
+      <c r="I52" s="62" t="s">
+        <v>371</v>
+      </c>
       <c r="J52" s="21">
         <v>4</v>
       </c>
@@ -10777,8 +10778,8 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="12" t="s">
-        <v>191</v>
+      <c r="O52" s="62" t="s">
+        <v>189</v>
       </c>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
@@ -10794,32 +10795,32 @@
       <c r="C53" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="D53" s="63" t="s">
-        <v>354</v>
-      </c>
-      <c r="E53" s="62" t="s">
-        <v>373</v>
+      <c r="D53" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="F53" s="21">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H53" s="62" t="s">
-        <v>197</v>
-      </c>
-      <c r="I53" s="62" t="s">
-        <v>371</v>
+        <v>186</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="J53" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="62" t="s">
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="12" t="s">
         <v>189</v>
       </c>
       <c r="P53" s="7"/>
@@ -10827,6 +10828,7 @@
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
     </row>
     <row r="54" spans="1:21" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="11">
@@ -10840,22 +10842,22 @@
         <v>375</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="F54" s="21">
         <v>9</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>188</v>
+        <v>379</v>
       </c>
       <c r="J54" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="12"/>
@@ -10869,53 +10871,10 @@
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
-    </row>
-    <row r="55" spans="1:21" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11">
-        <v>44075</v>
-      </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="F55" s="21">
-        <v>9</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="J55" s="21">
-        <v>2</v>
-      </c>
-      <c r="K55" s="7"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="71"/>
-    </row>
-    <row r="57" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="72"/>
+      <c r="U54" s="71"/>
+    </row>
+    <row r="56" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="72"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180599999999998" footer="0.51180599999999998"/>

--- a/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
+++ b/test_codecept/e2e/documents/ccd-config-aat-xui-testCaseType_v2.dev.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sreekanth/work/moj/ex-ui/rpx-xui-webapp/test_codecept/e2e/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA2230-70FB-0945-B9DC-5ABB01D06A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9E78B9-F5BC-184B-A588-1DE12FBC30E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33480" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurisdiction" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="387">
   <si>
     <t>Jurisdiction</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>DIVORCE</t>
-  </si>
-  <si>
-    <t>Family Divorce</t>
   </si>
   <si>
     <t>Family Divorce: dissolution of marriage</t>
@@ -1287,6 +1284,12 @@
   </si>
   <si>
     <t>XUI Test Case type dev</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>CIVIL</t>
   </si>
 </sst>
 </file>
@@ -3068,14 +3071,14 @@
         <v>42736</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="62" t="s">
+        <v>386</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>385</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>18</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -3152,7 +3155,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -3174,16 +3177,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3197,13 +3200,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3212,13 +3215,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -3228,13 +3231,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>261</v>
       </c>
       <c r="F5" s="7"/>
     </row>
@@ -3244,13 +3247,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>263</v>
       </c>
       <c r="F6" s="7"/>
     </row>
@@ -3314,7 +3317,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -3346,38 +3349,38 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="I2" s="34"/>
       <c r="J2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="O2" s="34"/>
       <c r="P2" s="34"/>
@@ -3393,37 +3396,37 @@
         <v>12</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -3434,24 +3437,24 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -3464,24 +3467,24 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
@@ -3494,26 +3497,26 @@
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -3526,24 +3529,24 @@
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -3556,24 +3559,24 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -3586,24 +3589,24 @@
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -3616,24 +3619,24 @@
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -3646,26 +3649,26 @@
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3678,26 +3681,26 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3710,24 +3713,24 @@
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -3740,24 +3743,24 @@
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -3770,24 +3773,24 @@
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -3800,24 +3803,24 @@
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -3830,26 +3833,26 @@
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -3862,26 +3865,26 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>299</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>300</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -3913,7 +3916,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>1</v>
@@ -3935,16 +3938,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3955,16 +3958,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3973,13 +3976,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
@@ -4057,7 +4060,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>1</v>
@@ -4074,10 +4077,10 @@
     <row r="2" spans="1:6" ht="113" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="34"/>
       <c r="B2" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>307</v>
       </c>
       <c r="D2" s="34"/>
       <c r="E2" s="34"/>
@@ -4085,13 +4088,13 @@
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="41"/>
@@ -4178,7 +4181,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -4200,16 +4203,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>311</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4220,16 +4223,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4238,13 +4241,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>313</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>314</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
@@ -4256,13 +4259,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
@@ -4274,13 +4277,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="F6" s="21">
         <v>3</v>
@@ -4292,13 +4295,13 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="F7" s="21">
         <v>4</v>
@@ -4356,7 +4359,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -4381,25 +4384,25 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="52" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="52" t="s">
+      <c r="G2" s="50" t="s">
         <v>311</v>
       </c>
-      <c r="G2" s="50" t="s">
-        <v>312</v>
-      </c>
       <c r="H2" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="I2" s="51" t="s">
         <v>316</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4410,25 +4413,25 @@
         <v>11</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>215</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>141</v>
-      </c>
       <c r="I3" s="57" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4437,14 +4440,14 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E4" s="58"/>
       <c r="F4" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G4" s="21">
         <v>1</v>
@@ -4458,14 +4461,14 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="21">
         <v>2</v>
@@ -4479,17 +4482,17 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -4500,14 +4503,14 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="21">
         <v>4</v>
@@ -4521,14 +4524,14 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G8" s="21">
         <v>5</v>
@@ -4583,7 +4586,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>1</v>
@@ -4605,16 +4608,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4625,16 +4628,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4643,13 +4646,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
@@ -4661,13 +4664,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
@@ -4738,7 +4741,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -4761,13 +4764,13 @@
       </c>
       <c r="C2" s="34"/>
       <c r="D2" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4778,16 +4781,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="E3" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>327</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4870,7 +4873,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -4891,13 +4894,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4908,13 +4911,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4923,13 +4926,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4938,13 +4941,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4953,13 +4956,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4968,13 +4971,13 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4983,13 +4986,13 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5032,7 +5035,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -5054,16 +5057,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>340</v>
-      </c>
       <c r="E2" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5074,16 +5077,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>141</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5092,16 +5095,16 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5110,16 +5113,16 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5128,16 +5131,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5146,16 +5149,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5164,16 +5167,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5182,16 +5185,16 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5200,16 +5203,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5218,16 +5221,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5236,16 +5239,16 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5254,16 +5257,16 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5272,16 +5275,16 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5290,16 +5293,16 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5308,16 +5311,16 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5326,16 +5329,16 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5344,16 +5347,16 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5362,16 +5365,16 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5380,16 +5383,16 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5398,16 +5401,16 @@
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5416,16 +5419,16 @@
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5434,16 +5437,16 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5452,16 +5455,16 @@
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5470,16 +5473,16 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5488,16 +5491,16 @@
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5506,16 +5509,16 @@
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5524,16 +5527,16 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5542,16 +5545,16 @@
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D29" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5560,16 +5563,16 @@
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5578,16 +5581,16 @@
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F31" s="72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5616,7 +5619,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>1</v>
@@ -5632,22 +5635,22 @@
     </row>
     <row r="2" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5658,7 +5661,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>12</v>
@@ -5675,16 +5678,16 @@
         <v>44075</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" t="s">
         <v>360</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>361</v>
-      </c>
-      <c r="F4" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:6" customFormat="1" x14ac:dyDescent="0.2">
@@ -5692,16 +5695,16 @@
         <v>44075</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E5" t="s">
         <v>363</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>364</v>
-      </c>
-      <c r="F5" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5770,7 +5773,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -5792,16 +5795,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5812,16 +5815,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5830,16 +5833,16 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5848,16 +5851,16 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5866,16 +5869,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5884,16 +5887,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5902,16 +5905,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5920,16 +5923,16 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5938,16 +5941,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5956,16 +5959,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5993,7 +5996,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -6015,16 +6018,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6035,16 +6038,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6053,16 +6056,16 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6071,16 +6074,16 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6089,16 +6092,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6107,16 +6110,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6125,16 +6128,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6143,16 +6146,16 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6161,16 +6164,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6179,16 +6182,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6197,16 +6200,16 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6215,16 +6218,16 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6233,16 +6236,16 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6251,16 +6254,16 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -6290,7 +6293,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -6309,19 +6312,19 @@
       <c r="A2" s="32"/>
       <c r="B2" s="32"/>
       <c r="C2" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>347</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6332,19 +6335,19 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6353,19 +6356,19 @@
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G4" s="67" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6374,19 +6377,19 @@
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E5" s="66" t="s">
+        <v>367</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>333</v>
+      </c>
+      <c r="G5" s="67" t="s">
         <v>368</v>
-      </c>
-      <c r="F5" s="66" t="s">
-        <v>334</v>
-      </c>
-      <c r="G5" s="67" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6395,19 +6398,19 @@
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E6" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6416,19 +6419,19 @@
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E7" s="66" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6437,19 +6440,19 @@
       </c>
       <c r="B8" s="66"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F8" s="66" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G8" s="67" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6481,7 +6484,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -6509,22 +6512,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -6544,16 +6547,16 @@
         <v>14</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="I3" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6562,13 +6565,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>385</v>
-      </c>
       <c r="E4" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>16</v>
@@ -6576,7 +6579,7 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6674,7 +6677,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -6702,34 +6705,34 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6740,34 +6743,34 @@
         <v>11</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6776,22 +6779,22 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -6802,26 +6805,26 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -6832,26 +6835,26 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="H6" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -6862,24 +6865,24 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="F7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>67</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -6890,24 +6893,24 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -6918,24 +6921,24 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="F9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -6946,24 +6949,24 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -6974,24 +6977,24 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>78</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>79</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -7002,24 +7005,24 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -7030,26 +7033,26 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="F13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="H13" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -7060,22 +7063,22 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D14" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>87</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -7086,22 +7089,22 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D15" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -7112,22 +7115,22 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>93</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -7138,22 +7141,22 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -7164,22 +7167,22 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D18" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>97</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -7190,22 +7193,22 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D19" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -7216,22 +7219,22 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -7242,22 +7245,22 @@
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>104</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -7268,22 +7271,22 @@
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -7294,22 +7297,22 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>109</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -7320,22 +7323,22 @@
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D24" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -7346,24 +7349,24 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D25" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -7374,22 +7377,22 @@
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D26" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -7400,22 +7403,22 @@
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -7426,22 +7429,22 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D28" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -7452,22 +7455,22 @@
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D29" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>124</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -7478,22 +7481,22 @@
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -7504,22 +7507,22 @@
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -7530,22 +7533,22 @@
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D32" s="62" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" s="62" t="s">
         <v>373</v>
-      </c>
-      <c r="E32" s="62" t="s">
-        <v>374</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="68" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -7556,22 +7559,22 @@
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D33" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E33" s="70" t="s">
         <v>377</v>
       </c>
-      <c r="E33" s="70" t="s">
-        <v>378</v>
-      </c>
       <c r="G33" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7580,22 +7583,22 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D34" s="72" t="s">
+        <v>381</v>
+      </c>
+      <c r="E34" s="70" t="s">
         <v>382</v>
       </c>
-      <c r="E34" s="70" t="s">
-        <v>383</v>
-      </c>
       <c r="G34" s="72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7627,7 +7630,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="3" t="s">
@@ -7656,37 +7659,37 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="J2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="K2" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7697,37 +7700,37 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7736,22 +7739,22 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G4" s="21">
         <v>1</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="21">
@@ -7767,22 +7770,22 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G5" s="21">
         <v>1</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="21">
@@ -7798,22 +7801,22 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G6" s="21">
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="21">
@@ -7829,22 +7832,22 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="F7" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G7" s="21">
         <v>1</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="21">
@@ -7860,22 +7863,22 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G8" s="21">
         <v>1</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="21">
@@ -7891,22 +7894,22 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G9" s="21">
         <v>1</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="21">
@@ -7922,22 +7925,22 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G10" s="21">
         <v>1</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="21">
@@ -7953,22 +7956,22 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G11" s="21">
         <v>1</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="21">
@@ -7984,22 +7987,22 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="G12" s="21">
         <v>1</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="21">
@@ -8015,22 +8018,22 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G13" s="21">
         <v>1</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="21">
@@ -8046,22 +8049,22 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G14" s="21">
         <v>1</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="21">
@@ -8077,22 +8080,22 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G15" s="21">
         <v>1</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="21">
@@ -8108,22 +8111,22 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G16" s="21">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="21">
@@ -8139,22 +8142,22 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G17" s="21">
         <v>2</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="21">
@@ -8170,22 +8173,22 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G18" s="21">
         <v>1</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -8199,22 +8202,22 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G19" s="21">
         <v>1</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I19" s="22"/>
       <c r="J19" s="23"/>
@@ -8228,22 +8231,22 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G20" s="21">
         <v>1</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I20" s="25"/>
       <c r="J20" s="26"/>
@@ -8257,22 +8260,22 @@
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G21" s="21">
         <v>1</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="26"/>
@@ -8286,22 +8289,22 @@
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G22" s="21">
         <v>1</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I22" s="25"/>
       <c r="J22" s="26"/>
@@ -8315,22 +8318,22 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G23" s="21">
         <v>1</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I23" s="25"/>
       <c r="J23" s="26"/>
@@ -8344,22 +8347,22 @@
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G24" s="21">
         <v>1</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I24" s="25"/>
       <c r="J24" s="26"/>
@@ -8373,22 +8376,22 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G25" s="21">
         <v>1</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I25" s="25"/>
       <c r="J25" s="26"/>
@@ -8402,22 +8405,22 @@
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G26" s="21">
         <v>1</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I26" s="25"/>
       <c r="J26" s="26"/>
@@ -8431,22 +8434,22 @@
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G27" s="21">
         <v>1</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I27" s="25"/>
       <c r="J27" s="26"/>
@@ -8460,22 +8463,22 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G28" s="21">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I28" s="25"/>
       <c r="J28" s="26"/>
@@ -8489,22 +8492,22 @@
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="G29" s="21">
         <v>1</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I29" s="28"/>
       <c r="J29" s="29"/>
@@ -8518,19 +8521,19 @@
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="F30" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>148</v>
-      </c>
       <c r="H30" s="72" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -8570,7 +8573,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -8607,61 +8610,61 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="T2" s="8" t="s">
-        <v>169</v>
-      </c>
       <c r="U2" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8672,61 +8675,61 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="T3" s="9" t="s">
-        <v>184</v>
-      </c>
       <c r="U3" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8735,25 +8738,25 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
       </c>
       <c r="G4" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J4" s="21">
         <v>1</v>
@@ -8763,7 +8766,7 @@
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
@@ -8778,25 +8781,25 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H5" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J5" s="21">
         <v>1</v>
@@ -8806,7 +8809,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="7"/>
       <c r="O5" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -8821,25 +8824,25 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="21">
         <v>3</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J6" s="21">
         <v>1</v>
@@ -8849,7 +8852,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="7"/>
       <c r="O6" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
@@ -8864,25 +8867,25 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="21">
         <v>4</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H7" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J7" s="21">
         <v>1</v>
@@ -8892,7 +8895,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -8907,25 +8910,25 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" s="21">
         <v>5</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J8" s="21">
         <v>1</v>
@@ -8935,7 +8938,7 @@
       <c r="M8" s="12"/>
       <c r="N8" s="7"/>
       <c r="O8" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
@@ -8950,25 +8953,25 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" s="21">
         <v>6</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H9" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J9" s="21">
         <v>1</v>
@@ -8978,7 +8981,7 @@
       <c r="M9" s="12"/>
       <c r="N9" s="7"/>
       <c r="O9" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
@@ -8993,25 +8996,25 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="21">
         <v>7</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H10" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J10" s="21">
         <v>2</v>
@@ -9021,7 +9024,7 @@
       <c r="M10" s="12"/>
       <c r="N10" s="7"/>
       <c r="O10" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -9036,25 +9039,25 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="21">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J11" s="21">
         <v>2</v>
@@ -9064,7 +9067,7 @@
       <c r="M11" s="12"/>
       <c r="N11" s="7"/>
       <c r="O11" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -9079,25 +9082,25 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="21">
         <v>9</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J12" s="21">
         <v>2</v>
@@ -9106,10 +9109,10 @@
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
@@ -9124,25 +9127,25 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="21">
         <v>10</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J13" s="21">
         <v>2</v>
@@ -9152,7 +9155,7 @@
       <c r="M13" s="12"/>
       <c r="N13" s="7"/>
       <c r="O13" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -9167,25 +9170,25 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14" s="21">
         <v>12</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J14" s="21">
         <v>2</v>
@@ -9195,7 +9198,7 @@
       <c r="M14" s="12"/>
       <c r="N14" s="7"/>
       <c r="O14" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -9210,25 +9213,25 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" s="21">
         <v>13</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J15" s="21">
         <v>3</v>
@@ -9238,7 +9241,7 @@
       <c r="M15" s="12"/>
       <c r="N15" s="7"/>
       <c r="O15" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -9253,25 +9256,25 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="21">
         <v>14</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H16" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J16" s="21">
         <v>3</v>
@@ -9281,7 +9284,7 @@
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -9296,25 +9299,25 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="21">
         <v>15</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J17" s="21">
         <v>3</v>
@@ -9324,7 +9327,7 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -9339,25 +9342,25 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F18" s="21">
         <v>16</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H18" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J18" s="21">
         <v>3</v>
@@ -9367,7 +9370,7 @@
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
@@ -9382,25 +9385,25 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="21">
         <v>17</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J19" s="21">
         <v>3</v>
@@ -9410,7 +9413,7 @@
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -9425,25 +9428,25 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="21">
         <v>18</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J20" s="21">
         <v>3</v>
@@ -9453,7 +9456,7 @@
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
@@ -9468,22 +9471,22 @@
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F21" s="21">
         <v>20</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="21">
@@ -9494,7 +9497,7 @@
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
@@ -9509,22 +9512,22 @@
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22" s="21">
         <v>21</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="21">
@@ -9535,7 +9538,7 @@
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -9550,22 +9553,22 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F23" s="21">
         <v>22</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="21">
@@ -9576,7 +9579,7 @@
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
@@ -9591,22 +9594,22 @@
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F24" s="21">
         <v>23</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="21">
@@ -9617,7 +9620,7 @@
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
@@ -9632,22 +9635,22 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F25" s="21">
         <v>24</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="21">
@@ -9658,7 +9661,7 @@
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
@@ -9673,22 +9676,22 @@
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" s="21">
         <v>25</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="21">
@@ -9699,7 +9702,7 @@
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
@@ -9714,22 +9717,22 @@
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F27" s="21">
         <v>26</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="21">
@@ -9740,7 +9743,7 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
@@ -9755,25 +9758,25 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F28" s="21">
         <v>1</v>
       </c>
       <c r="G28" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="I28" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J28" s="21">
         <v>1</v>
@@ -9783,7 +9786,7 @@
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
@@ -9798,25 +9801,25 @@
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F29" s="21">
         <v>2</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H29" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J29" s="21">
         <v>1</v>
@@ -9826,7 +9829,7 @@
       <c r="M29" s="12"/>
       <c r="N29" s="7"/>
       <c r="O29" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
@@ -9841,25 +9844,25 @@
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F30" s="21">
         <v>3</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H30" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J30" s="21">
         <v>1</v>
@@ -9869,7 +9872,7 @@
       <c r="M30" s="12"/>
       <c r="N30" s="7"/>
       <c r="O30" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
@@ -9883,25 +9886,25 @@
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F31" s="21">
         <v>4</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J31" s="21">
         <v>1</v>
@@ -9911,7 +9914,7 @@
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -9925,25 +9928,25 @@
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32" s="21">
         <v>5</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H32" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J32" s="21">
         <v>1</v>
@@ -9953,7 +9956,7 @@
       <c r="M32" s="12"/>
       <c r="N32" s="7"/>
       <c r="O32" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
@@ -9967,25 +9970,25 @@
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33" s="21">
         <v>6</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H33" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I33" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J33" s="21">
         <v>1</v>
@@ -9995,7 +9998,7 @@
       <c r="M33" s="12"/>
       <c r="N33" s="7"/>
       <c r="O33" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
@@ -10009,25 +10012,25 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F34" s="21">
         <v>7</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H34" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J34" s="21">
         <v>2</v>
@@ -10037,7 +10040,7 @@
       <c r="M34" s="12"/>
       <c r="N34" s="7"/>
       <c r="O34" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
@@ -10051,25 +10054,25 @@
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F35" s="21">
         <v>8</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H35" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J35" s="21">
         <v>2</v>
@@ -10079,7 +10082,7 @@
       <c r="M35" s="12"/>
       <c r="N35" s="7"/>
       <c r="O35" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
@@ -10093,25 +10096,25 @@
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F36" s="21">
         <v>9</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H36" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J36" s="21">
         <v>2</v>
@@ -10121,7 +10124,7 @@
       <c r="M36" s="12"/>
       <c r="N36" s="7"/>
       <c r="O36" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
@@ -10135,25 +10138,25 @@
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37" s="21">
         <v>10</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J37" s="21">
         <v>2</v>
@@ -10163,7 +10166,7 @@
       <c r="M37" s="12"/>
       <c r="N37" s="7"/>
       <c r="O37" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
@@ -10177,25 +10180,25 @@
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" s="21">
         <v>12</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H38" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="J38" s="21">
         <v>2</v>
@@ -10205,7 +10208,7 @@
       <c r="M38" s="12"/>
       <c r="N38" s="7"/>
       <c r="O38" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
@@ -10219,25 +10222,25 @@
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F39" s="21">
         <v>13</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I39" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J39" s="21">
         <v>3</v>
@@ -10247,7 +10250,7 @@
       <c r="M39" s="12"/>
       <c r="N39" s="7"/>
       <c r="O39" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
@@ -10261,25 +10264,25 @@
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F40" s="21">
         <v>14</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H40" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J40" s="21">
         <v>3</v>
@@ -10289,7 +10292,7 @@
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
@@ -10303,25 +10306,25 @@
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" s="21">
         <v>15</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H41" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J41" s="21">
         <v>3</v>
@@ -10331,7 +10334,7 @@
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
@@ -10345,25 +10348,25 @@
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F42" s="21">
         <v>16</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H42" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J42" s="21">
         <v>3</v>
@@ -10373,7 +10376,7 @@
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
@@ -10387,25 +10390,25 @@
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" s="21">
         <v>17</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H43" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J43" s="21">
         <v>3</v>
@@ -10415,7 +10418,7 @@
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
@@ -10429,25 +10432,25 @@
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" s="21">
         <v>18</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H44" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="J44" s="21">
         <v>3</v>
@@ -10457,7 +10460,7 @@
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
       <c r="O44" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
@@ -10471,22 +10474,22 @@
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F45" s="21">
         <v>20</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="21">
@@ -10497,7 +10500,7 @@
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
       <c r="O45" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
@@ -10511,22 +10514,22 @@
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="21">
         <v>21</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="21">
@@ -10537,7 +10540,7 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
@@ -10551,22 +10554,22 @@
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F47" s="21">
         <v>22</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="21">
@@ -10577,7 +10580,7 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
@@ -10591,22 +10594,22 @@
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F48" s="21">
         <v>23</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="21">
@@ -10617,7 +10620,7 @@
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P48" s="7"/>
       <c r="Q48" s="7"/>
@@ -10631,22 +10634,22 @@
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F49" s="21">
         <v>24</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="21">
@@ -10657,7 +10660,7 @@
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
       <c r="O49" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
@@ -10671,22 +10674,22 @@
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F50" s="21">
         <v>25</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="21">
@@ -10697,7 +10700,7 @@
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
       <c r="O50" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
@@ -10711,22 +10714,22 @@
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F51" s="21">
         <v>26</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I51" s="12"/>
       <c r="J51" s="21">
@@ -10737,7 +10740,7 @@
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
@@ -10751,25 +10754,25 @@
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D52" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F52" s="21">
         <v>28</v>
       </c>
       <c r="G52" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="H52" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" s="62" t="s">
         <v>370</v>
-      </c>
-      <c r="H52" s="62" t="s">
-        <v>197</v>
-      </c>
-      <c r="I52" s="62" t="s">
-        <v>371</v>
       </c>
       <c r="J52" s="21">
         <v>4</v>
@@ -10779,7 +10782,7 @@
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
       <c r="O52" s="62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
@@ -10793,25 +10796,25 @@
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F53" s="21">
         <v>9</v>
       </c>
       <c r="G53" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="I53" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J53" s="21">
         <v>1</v>
@@ -10821,7 +10824,7 @@
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
       <c r="O53" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
@@ -10836,25 +10839,25 @@
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F54" s="21">
         <v>9</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J54" s="21">
         <v>2</v>
@@ -10864,7 +10867,7 @@
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
       <c r="O54" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
@@ -10907,7 +10910,7 @@
   <sheetData>
     <row r="1" spans="1:256" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -11179,32 +11182,32 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>200</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>201</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>203</v>
-      </c>
       <c r="J2" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>157</v>
-      </c>
       <c r="L2" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -11462,31 +11465,31 @@
         <v>12</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="K3" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -11739,20 +11742,20 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G4" s="7"/>
       <c r="K4" s="62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L4" s="7"/>
     </row>
@@ -11762,20 +11765,20 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G5" s="65"/>
       <c r="K5" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:256" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -11784,25 +11787,25 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K6" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:256" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -11811,25 +11814,25 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G7" s="65"/>
       <c r="K7" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:256" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K10" s="64" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -11859,7 +11862,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -11883,22 +11886,22 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11909,7 +11912,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>12</v>
@@ -11921,10 +11924,10 @@
         <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11933,16 +11936,16 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>218</v>
-      </c>
       <c r="F4" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G4" s="21">
         <v>1</v>
@@ -11955,16 +11958,16 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>220</v>
-      </c>
       <c r="F5" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G5" s="21">
         <v>2</v>
@@ -11977,16 +11980,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>222</v>
-      </c>
       <c r="F6" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G6" s="21">
         <v>3</v>
@@ -12061,7 +12064,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -12097,58 +12100,58 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -12159,7 +12162,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>12</v>
@@ -12171,46 +12174,46 @@
         <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="J3" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="K3" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="L3" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="M3" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="N3" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="O3" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="P3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="P3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12219,23 +12222,23 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G4" s="21">
         <v>1</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -12244,13 +12247,13 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -12261,25 +12264,25 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G5" s="21">
         <v>2</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="7"/>
@@ -12288,13 +12291,13 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="R5" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -12305,25 +12308,25 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D6" s="62" t="s">
+        <v>353</v>
+      </c>
+      <c r="E6" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="F6" s="62" t="s">
         <v>355</v>
-      </c>
-      <c r="F6" s="62" t="s">
-        <v>356</v>
       </c>
       <c r="G6" s="21">
         <v>3</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="7"/>
@@ -12332,13 +12335,13 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="R6" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="R6" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -12349,25 +12352,25 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>376</v>
-      </c>
       <c r="F7" s="62" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G7" s="21">
         <v>3</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="7"/>
@@ -12376,13 +12379,13 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q7" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="R7" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
